--- a/output/Аэрофлот статус 21.08.2026.xlsx
+++ b/output/Аэрофлот статус 21.08.2026.xlsx
@@ -33637,7 +33637,7 @@
         <v/>
       </c>
       <c r="BB44" s="30" t="n">
-        <v/>
+        <v>3645154730</v>
       </c>
       <c r="BC44" s="30" t="n">
         <v/>
@@ -33651,8 +33651,10 @@
       <c r="BF44" s="30" t="n">
         <v/>
       </c>
-      <c r="BG44" s="30" t="n">
-        <v/>
+      <c r="BG44" s="30" t="inlineStr">
+        <is>
+          <t>DHL  в Турцию</t>
+        </is>
       </c>
       <c r="BH44" s="30" t="n">
         <v/>
@@ -36089,8 +36091,10 @@
       <c r="BE54" s="30" t="n">
         <v/>
       </c>
-      <c r="BF54" s="30" t="n">
-        <v/>
+      <c r="BF54" s="30" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG54" s="30" t="n">
         <v/>
@@ -37071,8 +37075,10 @@
       <c r="BE58" s="30" t="n">
         <v/>
       </c>
-      <c r="BF58" s="30" t="n">
-        <v/>
+      <c r="BF58" s="30" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG58" s="30" t="n">
         <v/>
@@ -37804,8 +37810,10 @@
       <c r="BE61" s="39" t="n">
         <v/>
       </c>
-      <c r="BF61" s="39" t="n">
-        <v/>
+      <c r="BF61" s="39" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG61" s="39" t="n">
         <v/>
